--- a/mlef_pipeline/results/OS_6/C23/training_summary.xlsx
+++ b/mlef_pipeline/results/OS_6/C23/training_summary.xlsx
@@ -847,7 +847,7 @@
         <v>0.6967034579270495</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04291756650123968</v>
+        <v>0.04291756650123957</v>
       </c>
       <c r="D6" t="n">
         <v>0.6254432925568406</v>
@@ -944,7 +944,7 @@
         <v>0.6804016620498616</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1005420351680771</v>
+        <v>0.100542035168077</v>
       </c>
       <c r="L7" t="n">
         <v>0.5928571428571429</v>
